--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -3325,7 +3325,7 @@
     <t>Twisted Wonderland</t>
   </si>
   <si>
-    <t>Ultrakill</t>
+    <t>ULTRAKILL</t>
   </si>
   <si>
     <t>Umineko - When They Cry</t>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1176</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1177">
   <si>
     <t>en</t>
   </si>
@@ -2411,6 +2411,9 @@
   </si>
   <si>
     <t>Open Source Objects</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -3891,7 +3894,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1175"/>
+  <dimension ref="A1:B1176"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13298,8 +13301,16 @@
         <v>1175</v>
       </c>
     </row>
+    <row r="1176" spans="1:2">
+      <c r="A1176" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>1176</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1175"/>
+  <autoFilter ref="A1:B1176"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1178">
   <si>
     <t>en</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>Chalice</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -3894,7 +3897,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1176"/>
+  <dimension ref="A1:B1177"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13309,8 +13312,16 @@
         <v>1176</v>
       </c>
     </row>
+    <row r="1177" spans="1:2">
+      <c r="A1177" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>1177</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1176"/>
+  <autoFilter ref="A1:B1177"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1179">
   <si>
     <t>en</t>
   </si>
@@ -2609,6 +2609,9 @@
   </si>
   <si>
     <t>Pop Team Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -3897,7 +3900,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13320,8 +13323,16 @@
         <v>1177</v>
       </c>
     </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>1178</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1180">
   <si>
     <t>en</t>
   </si>
@@ -3254,6 +3254,9 @@
   </si>
   <si>
     <t>Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -3900,7 +3903,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13331,8 +13334,16 @@
         <v>1178</v>
       </c>
     </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>1179</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1183</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1184">
   <si>
     <t>en</t>
   </si>
@@ -1759,6 +1759,9 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -1771,6 +1774,9 @@
     <t>Hypixel (Gear)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -1780,10 +1786,16 @@
     <t>Hypixel (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
     <t>Hypixel (Reforge Stone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -3903,7 +3915,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1183"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13342,8 +13354,40 @@
         <v>1179</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>1183</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1183"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1184</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1185">
   <si>
     <t>en</t>
   </si>
@@ -2663,6 +2663,9 @@
   </si>
   <si>
     <t>Prof Layton</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -3915,7 +3918,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1183"/>
+  <dimension ref="A1:B1184"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13386,8 +13389,16 @@
         <v>1183</v>
       </c>
     </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>1184</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1183"/>
+  <autoFilter ref="A1:B1184"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1185</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1186">
   <si>
     <t>en</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Baka and Test</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -3918,7 +3921,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1184"/>
+  <dimension ref="A1:B1185"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13397,8 +13400,16 @@
         <v>1184</v>
       </c>
     </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>1185</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1184"/>
+  <autoFilter ref="A1:B1185"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1187">
   <si>
     <t>en</t>
   </si>
@@ -2864,6 +2864,9 @@
   </si>
   <si>
     <t>Shadows of Mordor</t>
+  </si>
+  <si>
+    <t>Shark</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -3921,7 +3924,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1185"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13408,8 +13411,16 @@
         <v>1185</v>
       </c>
     </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>1186</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1185"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1188">
   <si>
     <t>en</t>
   </si>
@@ -992,6 +992,9 @@
   </si>
   <si>
     <t>Fairy Tales</t>
+  </si>
+  <si>
+    <t>Fall Drop</t>
   </si>
   <si>
     <t>Fall Guys</t>
@@ -3924,7 +3927,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13419,8 +13422,16 @@
         <v>1186</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>1187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1189">
   <si>
     <t>en</t>
   </si>
@@ -2654,6 +2654,9 @@
   </si>
   <si>
     <t>Predator</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
   </si>
   <si>
     <t>Present</t>
@@ -3927,7 +3930,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13430,8 +13433,16 @@
         <v>1187</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>1188</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1190">
   <si>
     <t>en</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Back to the Future</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -3930,7 +3933,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13441,8 +13444,16 @@
         <v>1188</v>
       </c>
     </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>1189</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1191">
   <si>
     <t>en</t>
   </si>
@@ -785,6 +785,9 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -3933,7 +3936,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13452,8 +13455,16 @@
         <v>1189</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>1190</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1192">
   <si>
     <t>en</t>
   </si>
@@ -1262,6 +1262,9 @@
   </si>
   <si>
     <t>Font (Orange)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -3936,7 +3939,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13463,8 +13466,16 @@
         <v>1190</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>1191</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -1000,9 +1000,6 @@
     <t>Fairy Tales</t>
   </si>
   <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -3512,6 +3509,9 @@
   </si>
   <si>
     <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Wilderness Bound</t>
   </si>
   <si>
     <t>Wings of Fire</t>
